--- a/trialLoopConditionsTeamprojekt.xlsx
+++ b/trialLoopConditionsTeamprojekt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Teamprojekt_Testphase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AB7ACC-B1E9-46CB-BF52-AD29B3CC2D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F4F2B-9C37-4868-96DC-9D5121026CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{41C89A80-5F4A-4DC4-B3AA-40BA250EFC97}"/>
   </bookViews>
